--- a/artfynd/S 2721-2022 artfynd.xlsx
+++ b/artfynd/S 2721-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135890601</v>
       </c>
       <c r="B2" t="n">
-        <v>107737</v>
+        <v>107739</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>135891121</v>
       </c>
       <c r="B3" t="n">
-        <v>103804</v>
+        <v>103806</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>135822202</v>
       </c>
       <c r="B4" t="n">
-        <v>107737</v>
+        <v>107739</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 2721-2022 artfynd.xlsx
+++ b/artfynd/S 2721-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135890601</v>
       </c>
       <c r="B2" t="n">
-        <v>107739</v>
+        <v>107762</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>135891121</v>
       </c>
       <c r="B3" t="n">
-        <v>103806</v>
+        <v>103826</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>135822202</v>
       </c>
       <c r="B4" t="n">
-        <v>107739</v>
+        <v>107762</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 2721-2022 artfynd.xlsx
+++ b/artfynd/S 2721-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135890601</v>
       </c>
       <c r="B2" t="n">
-        <v>107762</v>
+        <v>107764</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>135891121</v>
       </c>
       <c r="B3" t="n">
-        <v>103826</v>
+        <v>103828</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>135822202</v>
       </c>
       <c r="B4" t="n">
-        <v>107762</v>
+        <v>107764</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 2721-2022 artfynd.xlsx
+++ b/artfynd/S 2721-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135890601</v>
       </c>
       <c r="B2" t="n">
-        <v>107764</v>
+        <v>107765</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>135891121</v>
       </c>
       <c r="B3" t="n">
-        <v>103828</v>
+        <v>103829</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>135822202</v>
       </c>
       <c r="B4" t="n">
-        <v>107764</v>
+        <v>107765</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 2721-2022 artfynd.xlsx
+++ b/artfynd/S 2721-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135890601</v>
       </c>
       <c r="B2" t="n">
-        <v>107765</v>
+        <v>107766</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>135891121</v>
       </c>
       <c r="B3" t="n">
-        <v>103829</v>
+        <v>103830</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>135822202</v>
       </c>
       <c r="B4" t="n">
-        <v>107765</v>
+        <v>107766</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 2721-2022 artfynd.xlsx
+++ b/artfynd/S 2721-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135890601</v>
       </c>
       <c r="B2" t="n">
-        <v>107766</v>
+        <v>107772</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>135891121</v>
       </c>
       <c r="B3" t="n">
-        <v>103830</v>
+        <v>103836</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>135822202</v>
       </c>
       <c r="B4" t="n">
-        <v>107766</v>
+        <v>107772</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 2721-2022 artfynd.xlsx
+++ b/artfynd/S 2721-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135890601</v>
       </c>
       <c r="B2" t="n">
-        <v>107772</v>
+        <v>107773</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>135891121</v>
       </c>
       <c r="B3" t="n">
-        <v>103836</v>
+        <v>103837</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>135822202</v>
       </c>
       <c r="B4" t="n">
-        <v>107772</v>
+        <v>107773</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 2721-2022 artfynd.xlsx
+++ b/artfynd/S 2721-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135890601</v>
       </c>
       <c r="B2" t="n">
-        <v>107773</v>
+        <v>107784</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>135891121</v>
       </c>
       <c r="B3" t="n">
-        <v>103837</v>
+        <v>103848</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>135822202</v>
       </c>
       <c r="B4" t="n">
-        <v>107773</v>
+        <v>107784</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 2721-2022 artfynd.xlsx
+++ b/artfynd/S 2721-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135890601</v>
       </c>
       <c r="B2" t="n">
-        <v>107784</v>
+        <v>107797</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>135891121</v>
       </c>
       <c r="B3" t="n">
-        <v>103848</v>
+        <v>103861</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>135822202</v>
       </c>
       <c r="B4" t="n">
-        <v>107784</v>
+        <v>107797</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 2721-2022 artfynd.xlsx
+++ b/artfynd/S 2721-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135890601</v>
       </c>
       <c r="B2" t="n">
-        <v>107797</v>
+        <v>107798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>135891121</v>
       </c>
       <c r="B3" t="n">
-        <v>103861</v>
+        <v>103862</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>135822202</v>
       </c>
       <c r="B4" t="n">
-        <v>107797</v>
+        <v>107798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 2721-2022 artfynd.xlsx
+++ b/artfynd/S 2721-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135890601</v>
       </c>
       <c r="B2" t="n">
-        <v>107798</v>
+        <v>107811</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>135891121</v>
       </c>
       <c r="B3" t="n">
-        <v>103862</v>
+        <v>103875</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>135822202</v>
       </c>
       <c r="B4" t="n">
-        <v>107798</v>
+        <v>107811</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 2721-2022 artfynd.xlsx
+++ b/artfynd/S 2721-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135890601</v>
       </c>
       <c r="B2" t="n">
-        <v>107811</v>
+        <v>107812</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>135891121</v>
       </c>
       <c r="B3" t="n">
-        <v>103875</v>
+        <v>103876</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
